--- a/DateBase/orders/Nhat 48_2026-3-25.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-25.xlsx
@@ -1121,6 +1121,9 @@
       <c r="G2" t="str">
         <v>02067.5152.5177.510101620.51021265351557101555510510355510545553535535555085105555205105150.53125185105185110</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
